--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-observation-naissance-document.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-observation-naissance-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,8 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Cette entrée rassemble les observations relatives à une naissance.
- - Elle peut-être utilisée comme 'component'; d'une entrée FR-Historique-de-la-grossesse (1.3.6.1.4.1.19376.1.5.3.1.4.13.5.1).</t>
+    <t>FrObservationNaissanceDocument est un profil qui permet de rassembler les observations relatives à une naissance.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -574,7 +573,7 @@
     <t>Observation.status</t>
   </si>
   <si>
-    <t>Statut de l’entrée</t>
+    <t>Statut de l'observation</t>
   </si>
   <si>
     <t>The status of the result value.</t>
@@ -651,7 +650,7 @@
 </t>
   </si>
   <si>
-    <t>Code de l'entrée.</t>
+    <t>Code de l'observation</t>
   </si>
   <si>
     <t>Describes what was observed. Sometimes this is called the observation "name".</t>
